--- a/electron/data/summary_portfolio2.xlsx
+++ b/electron/data/summary_portfolio2.xlsx
@@ -457,13 +457,13 @@
         <v>Equity</v>
       </c>
       <c r="C2" t="str">
-        <v>Mari Energies Limited</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>OIL &amp; GAS EXPLORATION COMPANIES</v>
+        <v/>
       </c>
       <c r="F2">
         <v>100</v>
@@ -473,18 +473,6 @@
       </c>
       <c r="H2">
         <v>500.8675</v>
-      </c>
-      <c r="I2">
-        <v>764.21</v>
-      </c>
-      <c r="J2">
-        <v>-6.66</v>
-      </c>
-      <c r="K2" t="str">
-        <v>(-0.86%)</v>
-      </c>
-      <c r="L2">
-        <v>52.57727842193795</v>
       </c>
       <c r="M2">
         <v>71.4282658376324</v>
@@ -522,16 +510,16 @@
         <v>200.35</v>
       </c>
       <c r="I3">
-        <v>230.1</v>
+        <v>231.73</v>
       </c>
       <c r="J3">
-        <v>0.47</v>
+        <v>2.1</v>
       </c>
       <c r="K3" t="str">
-        <v>(0.21%)</v>
+        <v>(0.92%)</v>
       </c>
       <c r="L3">
-        <v>14.849014225106064</v>
+        <v>15.662590466683302</v>
       </c>
       <c r="M3">
         <v>28.571734162367594</v>

--- a/electron/data/summary_portfolio2.xlsx
+++ b/electron/data/summary_portfolio2.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:O4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,9 +445,6 @@
       <c r="O1" t="str">
         <v>dividendIncome</v>
       </c>
-      <c r="P1" t="str">
-        <v>rawJson</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -457,13 +454,13 @@
         <v>Equity</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Mari Energies Limited</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>OIL &amp; GAS EXPLORATION COMPANIES</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -474,8 +471,20 @@
       <c r="H2">
         <v>500.8675</v>
       </c>
+      <c r="I2">
+        <v>753.74</v>
+      </c>
+      <c r="J2">
+        <v>-17.13</v>
+      </c>
+      <c r="K2" t="str">
+        <v>(-2.22%)</v>
+      </c>
+      <c r="L2">
+        <v>50.48690521944427</v>
+      </c>
       <c r="M2">
-        <v>71.4282658376324</v>
+        <v>71.30478260136398</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -510,30 +519,77 @@
         <v>200.35</v>
       </c>
       <c r="I3">
-        <v>231.73</v>
+        <v>233.16</v>
       </c>
       <c r="J3">
-        <v>2.1</v>
+        <v>3.53</v>
       </c>
       <c r="K3" t="str">
-        <v>(0.92%)</v>
+        <v>(1.54%)</v>
       </c>
       <c r="L3">
-        <v>15.662590466683302</v>
+        <v>16.376341402545545</v>
       </c>
       <c r="M3">
-        <v>28.571734162367594</v>
+        <v>28.522340128244046</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PAEL</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Equity</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Pak Elektron Limited</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v>CABLE &amp; ELECTRICAL GOODS</v>
+      </c>
+      <c r="F4">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>121.4345</v>
+      </c>
+      <c r="H4">
+        <v>11.0395</v>
+      </c>
+      <c r="I4">
+        <v>56.18</v>
+      </c>
+      <c r="J4">
+        <v>-2.08</v>
+      </c>
+      <c r="K4" t="str">
+        <v>(-3.57%)</v>
+      </c>
+      <c r="L4">
+        <v>408.8998595950904</v>
+      </c>
+      <c r="M4">
+        <v>0.1728772703919766</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/electron/data/summary_portfolio2.xlsx
+++ b/electron/data/summary_portfolio2.xlsx
@@ -484,7 +484,7 @@
         <v>50.48690521944427</v>
       </c>
       <c r="M2">
-        <v>71.30478260136398</v>
+        <v>52.6301686896376</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -531,7 +531,7 @@
         <v>16.376341402545545</v>
       </c>
       <c r="M3">
-        <v>28.522340128244046</v>
+        <v>21.052382709936047</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -557,13 +557,13 @@
         <v>CABLE &amp; ELECTRICAL GOODS</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="G4">
-        <v>121.4345</v>
+        <v>25045.625</v>
       </c>
       <c r="H4">
-        <v>11.0395</v>
+        <v>50.09125</v>
       </c>
       <c r="I4">
         <v>56.18</v>
@@ -575,10 +575,10 @@
         <v>(-3.57%)</v>
       </c>
       <c r="L4">
-        <v>408.8998595950904</v>
+        <v>12.155316547301169</v>
       </c>
       <c r="M4">
-        <v>0.1728772703919766</v>
+        <v>26.317448600426353</v>
       </c>
       <c r="N4">
         <v>0</v>

--- a/electron/data/summary_portfolio2.xlsx
+++ b/electron/data/summary_portfolio2.xlsx
@@ -472,16 +472,16 @@
         <v>500.8675</v>
       </c>
       <c r="I2">
-        <v>753.74</v>
+        <v>746.49</v>
       </c>
       <c r="J2">
-        <v>-17.13</v>
+        <v>6.41</v>
       </c>
       <c r="K2" t="str">
-        <v>(-2.22%)</v>
+        <v>(0.87%)</v>
       </c>
       <c r="L2">
-        <v>50.48690521944427</v>
+        <v>49.039416612177874</v>
       </c>
       <c r="M2">
         <v>52.6301686896376</v>
@@ -519,16 +519,16 @@
         <v>200.35</v>
       </c>
       <c r="I3">
-        <v>233.16</v>
+        <v>236</v>
       </c>
       <c r="J3">
-        <v>3.53</v>
+        <v>2.08</v>
       </c>
       <c r="K3" t="str">
-        <v>(1.54%)</v>
+        <v>(0.89%)</v>
       </c>
       <c r="L3">
-        <v>16.376341402545545</v>
+        <v>17.79386074369853</v>
       </c>
       <c r="M3">
         <v>21.052382709936047</v>
@@ -566,16 +566,16 @@
         <v>50.09125</v>
       </c>
       <c r="I4">
-        <v>56.18</v>
+        <v>55.75</v>
       </c>
       <c r="J4">
-        <v>-2.08</v>
+        <v>0.88</v>
       </c>
       <c r="K4" t="str">
-        <v>(-3.57%)</v>
+        <v>(1.60%)</v>
       </c>
       <c r="L4">
-        <v>12.155316547301169</v>
+        <v>11.296883188181564</v>
       </c>
       <c r="M4">
         <v>26.317448600426353</v>
